--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>60428.51</v>
+        <v>59976.26</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>55324.7</v>
+        <v>54910.65</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>55324.7</v>
+        <v>54910.65</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>46345.79</v>
+        <v>45998.94</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>28492.26</v>
+        <v>28372.13</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37571.1</v>
+        <v>37912.84</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>52168.28</v>
+        <v>52642.79</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>59360.57</v>
+        <v>59900.5</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46948.8</v>
+        <v>47375.83</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>38225.45</v>
+        <v>38491.58</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27293.16</v>
+        <v>27483.18</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>33770.56</v>
+        <v>34005.68</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>63090.62</v>
+        <v>63506.13</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15309.04</v>
+        <v>15409.86</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>68209.44</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11474.21</v>
+        <v>11454.55</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40651.96</v>
+        <v>40610.03</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>40215.17</v>
+        <v>39927.07</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26084.14</v>
+        <v>26045.77</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31520.15</v>
+        <v>31348.5</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>80430.33</v>
+        <v>79992.33</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>29547.92</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37571.1</v>
+        <v>37349.69</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>220060.09</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="26">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>124329.61</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="27">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>155676.55</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26305.98</v>
+        <v>26204.45</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>22948.42</v>
+        <v>22859.85</v>
       </c>
     </row>
     <row r="30">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>51536.01</v>
+        <v>51337.1</v>
       </c>
     </row>
     <row r="31">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>50511.59</v>
+        <v>50773.11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -758,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>656-36-CM26</t>
+          <t>2369-128-SE25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +789,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,43 +799,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>28372.13</v>
+        <v>389190.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5153-262-CM26</t>
+          <t>656-36-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,53 +854,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37912.84</v>
+        <v>28372.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3287-67-CM26</t>
+          <t>5153-262-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,43 +929,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>52642.79</v>
+        <v>37912.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3287-68-CM26</t>
+          <t>3287-67-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -981,28 +1009,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>59900.5</v>
+        <v>52642.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3671-14-CM26</t>
+          <t>3287-68-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,27 +1059,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1089,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47375.83</v>
+        <v>59900.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2702-53-CM26</t>
+          <t>3671-14-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1110,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,43 +1120,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>38491.58</v>
+        <v>47375.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2745-17-CM26</t>
+          <t>2702-53-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,22 +1180,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1172,20 +1208,24 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27483.18</v>
+        <v>38491.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3775-13-CM26</t>
+          <t>2745-17-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,43 +1250,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>34005.68</v>
+        <v>27483.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2410-5-CM26</t>
+          <t>3775-13-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1305,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,32 +1315,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,13 +1349,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>63506.13</v>
+        <v>34005.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2675-41-CM26</t>
+          <t>2410-5-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1336,43 +1380,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15409.86</v>
+        <v>63506.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3820-123-CM26</t>
+          <t>2675-41-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1435,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,43 +1445,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>68816.96000000001</v>
+        <v>15409.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1426037-23-CM26</t>
+          <t>3820-123-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,7 +1500,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,43 +1510,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11454.55</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4451-105-CM26</t>
+          <t>1426037-23-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1565,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,43 +1575,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40610.03</v>
+        <v>11454.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2898-4-CM26</t>
+          <t>4451-105-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,7 +1630,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,43 +1640,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39927.07</v>
+        <v>40610.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1456837-6-CM26</t>
+          <t>2898-4-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1695,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,43 +1705,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.981.450-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LA QUEBRADA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26045.77</v>
+        <v>39927.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3963-5-CM26</t>
+          <t>1456837-6-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,53 +1760,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.080.900-1</t>
+          <t>61.981.450-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEUMO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LA QUEBRADA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31348.5</v>
+        <v>26045.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4052-19-CM26</t>
+          <t>3963-5-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,48 +1830,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.080.900-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>I MUNICIPALIDAD DE PEUMO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>79992.33</v>
+        <v>31348.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3820-139-CM26</t>
+          <t>4052-19-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1824,43 +1900,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>29387.01</v>
+        <v>79992.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3793-22-CM26</t>
+          <t>3820-139-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1955,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,43 +1965,47 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.090.400-4</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37349.69</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>3793-22-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,42 +2020,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.090.400-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1980,13 +2064,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>218722.92</v>
+        <v>37349.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>2369-117-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2006,37 +2090,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2045,13 +2129,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>123574.14</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>1596-40-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2091,17 +2175,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2110,13 +2194,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>154730.6</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1107276-37-CM26</t>
+          <t>1596-42-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2131,7 +2215,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2141,43 +2225,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26204.45</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3658-84-CM26</t>
+          <t>1107276-37-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2202,27 +2290,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.072.800-1</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2232,13 +2320,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>22859.85</v>
+        <v>26204.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3661-133-CM26</t>
+          <t>3658-84-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2263,97 +2351,170 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.072.800-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>51337.1</v>
+        <v>22859.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>3661-133-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.051.400-1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>51337.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>29-1421-CM26</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2239-8-LR23</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>61.103.035-5</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>50773.11</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
